--- a/intake_forms/042_mpox_intake_form--intake_forms.xlsx
+++ b/intake_forms/042_mpox_intake_form--intake_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -815,8 +815,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'none',_'name':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'None', 'name': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'local_emergency_room',_'name':_'local_emergency_room',_'hint':_none}</t>
+          <t>local_emergency_room</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Local Emergency Room', 'name': 'Local Emergency Room', 'hint': None}</t>
+          <t>Local Emergency Room</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'primary_care_center',_'name':_'primary_care_center',_'hint':_none}</t>
+          <t>primary_care_center</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'Primary Care Center', 'name': 'Primary Care Center', 'hint': None}</t>
+          <t>Primary Care Center</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'urgent_care',_'name':_'urgent_care',_'hint':_none}</t>
+          <t>urgent_care</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'Urgent Care', 'name': 'Urgent Care', 'hint': None}</t>
+          <t>Urgent Care</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'name':_'other',_'hint':_'specify'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'Other', 'name': 'Other', 'hint': 'Specify'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'patient',_'name':_'patient',_'hint':_none}</t>
+          <t>patient</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'Patient', 'name': 'Patient', 'hint': None}</t>
+          <t>Patient</t>
         </is>
       </c>
     </row>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'physician',_'name':_'physician',_'hint':_none}</t>
+          <t>physician</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'Physician', 'name': 'Physician', 'hint': None}</t>
+          <t>Physician</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1371,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'name':_'other',_'hint':_'specify'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'Other', 'name': 'Other', 'hint': 'Specify'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
